--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487187_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487187_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.027799999999999</v>
+        <v>9.7615</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9973</v>
+        <v>8.5168</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0306</v>
+        <v>1.2447</v>
       </c>
       <c r="G2" t="n">
         <v>7.4246</v>
@@ -610,13 +610,13 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7133</v>
+        <v>-0.9796</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4481</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2652</v>
+        <v>-1.051</v>
       </c>
       <c r="V2" t="n">
         <v>1.5795</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1119</v>
+        <v>3.6617</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2505</v>
+        <v>3.3434</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8614</v>
+        <v>0.3183</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3121</v>
+        <v>3.0333</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3787</v>
+        <v>1.6395</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6908</v>
+        <v>1.3938</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7385</v>
+        <v>3.2125</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5903</v>
+        <v>1.7801</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3288</v>
+        <v>1.4323</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4264</v>
+        <v>-0.1792</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7884</v>
+        <v>-0.1406</v>
       </c>
       <c r="O3" t="n">
-        <v>0.362</v>
+        <v>-0.0386</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3511</v>
+        <v>3.0881</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.8252</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4741</v>
+        <v>3.0881</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0998</v>
+        <v>-1.5176</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3517</v>
+        <v>-0.155</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2519</v>
+        <v>-1.3627</v>
       </c>
       <c r="V3" t="n">
-        <v>3.0511</v>
+        <v>-0.9421</v>
       </c>
       <c r="W3" t="n">
-        <v>2.9854</v>
+        <v>0.2859</v>
       </c>
       <c r="X3" t="n">
-        <v>0.06560000000000001</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4541</v>
+        <v>3.3673</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3231</v>
+        <v>1.2286</v>
       </c>
       <c r="F4" t="n">
-        <v>0.131</v>
+        <v>2.1387</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0333</v>
+        <v>2.3121</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6395</v>
+        <v>-1.3787</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3938</v>
+        <v>3.6908</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2125</v>
+        <v>2.7385</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7801</v>
+        <v>-0.5903</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4323</v>
+        <v>3.3288</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1792</v>
+        <v>-0.4264</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1406</v>
+        <v>-0.7884</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0386</v>
+        <v>0.362</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0881</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0881</v>
+        <v>3.4741</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.7253</v>
+        <v>-0.6448</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1752</v>
+        <v>0.3299</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.5501</v>
+        <v>-0.9747</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9421</v>
+        <v>3.0511</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2859</v>
+        <v>2.9854</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8755</v>
+        <v>2.869</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6386</v>
+        <v>2.4179</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2369</v>
+        <v>0.4511</v>
       </c>
       <c r="G5" t="n">
         <v>0.8109</v>
@@ -844,13 +844,13 @@
         <v>3.6672</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.5144</v>
+        <v>-1.5209</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.805</v>
+        <v>-0.0257</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.7094</v>
+        <v>-1.4952</v>
       </c>
       <c r="V5" t="n">
         <v>1.842</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0063</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0835</v>
+        <v>-0.4246</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0898</v>
+        <v>1.1166</v>
       </c>
       <c r="G6" t="n">
         <v>0.2863</v>
@@ -922,13 +922,13 @@
         <v>2.7021</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7542</v>
+        <v>-1.0685</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3385</v>
+        <v>-0.0026</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0926</v>
+        <v>-1.0659</v>
       </c>
       <c r="V6" t="n">
         <v>-1.228</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2057</v>
+        <v>-2.0826</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9943</v>
+        <v>2.0104</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.2</v>
+        <v>-4.0929</v>
       </c>
       <c r="G8" t="n">
         <v>0.6882</v>
@@ -1078,13 +1078,13 @@
         <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8595</v>
+        <v>0.9826</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2323</v>
+        <v>1.2483</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3728</v>
+        <v>-0.2657</v>
       </c>
       <c r="V8" t="n">
         <v>-3.9464</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MARCOS SÁNCHEZ</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2137</v>
+        <v>-2.2668</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1073</v>
+        <v>-0.1178</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1064</v>
+        <v>-2.149</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2581</v>
+        <v>-1.0229</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4116</v>
+        <v>0.7907</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8464</v>
+        <v>-1.8136</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3834</v>
+        <v>0.3917</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5434</v>
+        <v>1.6455</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.84</v>
+        <v>-1.2538</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8747</v>
+        <v>-1.4146</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8682</v>
+        <v>-0.8548</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0064</v>
+        <v>-0.5598</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.386</v>
+        <v>0.965</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1368</v>
+        <v>-0.1044</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0132</v>
+        <v>0.1468</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1236</v>
+        <v>-0.2512</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2936</v>
+        <v>-2.1044</v>
       </c>
       <c r="W9" t="n">
-        <v>1.228</v>
+        <v>-0.6562</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06560000000000001</v>
+        <v>-1.4482</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>A. MARCOS SÁNCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3415</v>
+        <v>-2.3951</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9784</v>
+        <v>-2.0478</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3631</v>
+        <v>-0.3474</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0229</v>
+        <v>-3.2581</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7907</v>
+        <v>-1.4116</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8136</v>
+        <v>-1.8464</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3917</v>
+        <v>-2.3834</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6455</v>
+        <v>-0.5434</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2538</v>
+        <v>-1.84</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4146</v>
+        <v>-0.8747</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8548</v>
+        <v>-0.8682</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5598</v>
+        <v>-0.0064</v>
       </c>
       <c r="P10" t="n">
-        <v>0.965</v>
+        <v>-0.386</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1792</v>
+        <v>-0.0446</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7139</v>
+        <v>0.0727</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4653</v>
+        <v>-0.1173</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1044</v>
+        <v>1.2936</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6562</v>
+        <v>1.228</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4482</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.8482</v>
+        <v>13.7405</v>
       </c>
       <c r="E11" t="n">
-        <v>14.0346</v>
+        <v>14.9269</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1863</v>
+        <v>-1.1864</v>
       </c>
       <c r="G11" t="n">
         <v>10.4079</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2329999999999998</v>
+        <v>0.2329999999999994</v>
       </c>
       <c r="I11" t="n">
         <v>10.1749</v>
@@ -1288,7 +1288,7 @@
         <v>13.6071</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2072</v>
+        <v>3.207199999999999</v>
       </c>
       <c r="L11" t="n">
         <v>10.3998</v>
@@ -1303,7 +1303,7 @@
         <v>-0.225</v>
       </c>
       <c r="P11" t="n">
-        <v>8.6853</v>
+        <v>8.685300000000002</v>
       </c>
       <c r="Q11" t="n">
         <v>-9.6503</v>
@@ -1312,16 +1312,16 @@
         <v>18.3356</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.7903</v>
+        <v>-4.8978</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7934999999999997</v>
+        <v>1.6858</v>
       </c>
       <c r="U11" t="n">
-        <v>-6.5837</v>
+        <v>-6.583699999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4547000000000008</v>
+        <v>-0.4547000000000003</v>
       </c>
       <c r="W11" t="n">
         <v>9.2845</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.1305</v>
+        <v>10.3388</v>
       </c>
       <c r="E12" t="n">
-        <v>9.7738</v>
+        <v>10.8753</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6433</v>
+        <v>-0.5366</v>
       </c>
       <c r="G12" t="n">
         <v>6.0651</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2095</v>
+        <v>0.9987</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1956</v>
+        <v>0.9059</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0139</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>4.626</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5545</v>
+        <v>1.5277</v>
       </c>
       <c r="E13" t="n">
         <v>0.9548</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5997</v>
+        <v>0.5729</v>
       </c>
       <c r="G13" t="n">
         <v>1.4084</v>
@@ -1468,13 +1468,13 @@
         <v>0.193</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0469</v>
+        <v>-0.0737</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0126</v>
+        <v>-0.0142</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>A. RUIZ FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1822</v>
+        <v>-0.0595</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7466</v>
+        <v>-0.0595</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9288</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.7206</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2358</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4848</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.1141</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.1955</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0814</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6065</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0403</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5662</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3511</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5977</v>
+        <v>-0.0595</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2976</v>
+        <v>-0.0595</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3001</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. RUIZ FERNÁNDEZ</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0595</v>
+        <v>-0.4273</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0595</v>
+        <v>0.0226</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0.4498</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.112</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0.1055</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-0.0064</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.0414</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.0414</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0.1534</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.1469</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.0064</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0595</v>
+        <v>-0.3153</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0595</v>
+        <v>-0.0188</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0.2965</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.408</v>
+        <v>-0.8413</v>
       </c>
       <c r="E16" t="n">
-        <v>0.532</v>
+        <v>-0.169</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.6723</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9756</v>
@@ -1702,13 +1702,13 @@
         <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8534</v>
+        <v>1.4201</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2236</v>
+        <v>1.5226</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3702</v>
+        <v>-0.1025</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5542</v>
+        <v>-1.2735</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0776</v>
+        <v>1.1659</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4766</v>
+        <v>-2.4394</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.112</v>
+        <v>-0.9819</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1055</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0064</v>
+        <v>-1.6215</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0414</v>
+        <v>0.5185</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0414</v>
+        <v>0.4863</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.0321</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1534</v>
+        <v>-1.5004</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1469</v>
+        <v>0.1533</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0064</v>
+        <v>-1.6537</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4422</v>
+        <v>0.4346</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.119</v>
+        <v>0.0757</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3232</v>
+        <v>0.3589</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.8842</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3757</v>
+        <v>-1.3539</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4649</v>
+        <v>-2.1486</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8406</v>
+        <v>0.7946</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9819</v>
+        <v>-1.7206</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6395999999999999</v>
+        <v>-1.2358</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6215</v>
+        <v>-0.4848</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5185</v>
+        <v>-1.1141</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4863</v>
+        <v>-1.1955</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0321</v>
+        <v>0.0814</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5004</v>
+        <v>-0.6065</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1533</v>
+        <v>-0.0403</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6537</v>
+        <v>-0.5662</v>
       </c>
       <c r="P18" t="n">
-        <v>1.158</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6676</v>
+        <v>1.0615</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6253</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0423</v>
+        <v>0.1659</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8842</v>
+        <v>0.6562</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4559</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1395</v>
+        <v>-3.0929</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7907</v>
+        <v>1.8909</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.9302</v>
+        <v>-4.9837</v>
       </c>
       <c r="G19" t="n">
         <v>2.0166</v>
@@ -1936,13 +1936,13 @@
         <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1877</v>
+        <v>0.2343</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0462</v>
+        <v>0.0539</v>
       </c>
       <c r="U19" t="n">
-        <v>0.234</v>
+        <v>0.1804</v>
       </c>
       <c r="V19" t="n">
         <v>-3.0277</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9418</v>
+        <v>-4.9915</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.371</v>
+        <v>-3.6763</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5707</v>
+        <v>-1.3152</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.83</v>
+        <v>-5.8329</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.864</v>
+        <v>-0.2122</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.966</v>
+        <v>-5.6207</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.8223</v>
+        <v>-3.9582</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.6499</v>
+        <v>0.6829</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1724</v>
+        <v>-4.6411</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0077</v>
+        <v>-1.8747</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2141</v>
+        <v>-0.8951</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7936</v>
+        <v>-0.9797</v>
       </c>
       <c r="P20" t="n">
-        <v>-5.9833</v>
+        <v>0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>-7.7203</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4735</v>
+        <v>0.5483</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2019</v>
+        <v>0.9611</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2716</v>
+        <v>-0.4128</v>
       </c>
       <c r="V20" t="n">
-        <v>3.398</v>
+        <v>-0.2859</v>
       </c>
       <c r="W20" t="n">
-        <v>3.9698</v>
+        <v>0.2859</v>
       </c>
       <c r="X20" t="n">
         <v>-0.5717</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6956</v>
+        <v>-5.3955</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1972</v>
+        <v>-1.8968</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4984</v>
+        <v>-3.4987</v>
       </c>
       <c r="G21" t="n">
         <v>-4.4449</v>
@@ -2092,13 +2092,13 @@
         <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1051</v>
+        <v>0.4052</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2062</v>
+        <v>0.5067</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1012</v>
+        <v>-0.1015</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1278</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.5412</v>
+        <v>-6.6117</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.878</v>
+        <v>-5.773</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6632</v>
+        <v>-0.8388</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.8329</v>
+        <v>-5.83</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2122</v>
+        <v>-2.864</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.6207</v>
+        <v>-2.966</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.9582</v>
+        <v>-3.8223</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6829</v>
+        <v>-2.6499</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.6411</v>
+        <v>-1.1724</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8747</v>
+        <v>-2.0077</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8951</v>
+        <v>-0.2141</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9797</v>
+        <v>-1.7936</v>
       </c>
       <c r="P22" t="n">
-        <v>0.579</v>
+        <v>-5.9833</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.965</v>
+        <v>-7.7203</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0014</v>
+        <v>1.8035</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2406</v>
+        <v>1.7999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7608</v>
+        <v>0.0036</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2859</v>
+        <v>3.398</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2859</v>
+        <v>3.9698</v>
       </c>
       <c r="X22" t="n">
         <v>-0.5717</v>
@@ -2203,31 +2203,31 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.8483</v>
+        <v>-12.1806</v>
       </c>
       <c r="E23" t="n">
-        <v>1.186299999999999</v>
+        <v>1.186300000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.0345</v>
+        <v>-13.367</v>
       </c>
       <c r="G23" t="n">
         <v>-10.4078</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2330999999999997</v>
+        <v>-0.2331000000000008</v>
       </c>
       <c r="I23" t="n">
         <v>-10.1746</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1994</v>
+        <v>3.199400000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9743</v>
+        <v>2.974300000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2250000000000005</v>
+        <v>0.2249999999999996</v>
       </c>
       <c r="M23" t="n">
         <v>-13.6073</v>
@@ -2239,25 +2239,25 @@
         <v>-10.3998</v>
       </c>
       <c r="P23" t="n">
-        <v>-8.685599999999999</v>
+        <v>-8.685600000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-18.3357</v>
       </c>
       <c r="R23" t="n">
-        <v>9.650399999999999</v>
+        <v>9.650400000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>5.7903</v>
+        <v>6.457700000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>6.583600000000001</v>
+        <v>6.5837</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7933000000000001</v>
+        <v>-0.1259</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4547000000000006</v>
+        <v>0.4547000000000003</v>
       </c>
       <c r="W23" t="n">
         <v>9.7393</v>
